--- a/docs/Matriz de trazabilidad.xlsx
+++ b/docs/Matriz de trazabilidad.xlsx
@@ -1,12 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\mercy-foods\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD75E35B-634B-448E-A0D7-26C831684D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Matriz de trazabilidad" sheetId="1" r:id="rId4"/>
+    <sheet name="Matriz de trazabilidad" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -298,85 +312,124 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF1B1C1D"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF444746"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -566,818 +619,822 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="49.5"/>
-    <col customWidth="1" min="3" max="3" width="35.5"/>
-    <col customWidth="1" min="4" max="4" width="69.0"/>
-    <col customWidth="1" min="5" max="5" width="32.25"/>
-    <col customWidth="1" min="6" max="6" width="54.63"/>
-    <col customWidth="1" min="7" max="7" width="47.38"/>
+    <col min="2" max="2" width="49.42578125" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" customWidth="1"/>
+    <col min="4" max="4" width="69" customWidth="1"/>
+    <col min="5" max="5" width="32.28515625" customWidth="1"/>
+    <col min="6" max="6" width="54.5703125" customWidth="1"/>
+    <col min="7" max="7" width="47.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+    </row>
+    <row r="3" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
-      <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+    </row>
+    <row r="4" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+    </row>
+    <row r="5" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+    </row>
+    <row r="6" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+    </row>
+    <row r="7" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+    </row>
+    <row r="10" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+    </row>
+    <row r="11" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-    </row>
-    <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+    </row>
+    <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+    </row>
+    <row r="13" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+    </row>
+    <row r="16" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
-      <c r="V18" s="4"/>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+    </row>
+    <row r="17" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+    </row>
+    <row r="18" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+    </row>
+    <row r="19" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+    </row>
+    <row r="20" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+    </row>
+    <row r="21" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>